--- a/results/02_taxa_assemblage/AU-Sweeping/tables/k3_popout_au_sweep_full.xlsx
+++ b/results/02_taxa_assemblage/AU-Sweeping/tables/k3_popout_au_sweep_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,54 +499,62 @@
           <t>newly_entered_site</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>is_atypical</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8919</v>
+        <v>0.9522</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0399</v>
+        <v>0.0139</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>0.881</v>
+        <v>0.5562</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0258</v>
+        <v>0.0034</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
-        <v>0.459</v>
+        <v>0.9606</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0124</v>
+        <v>0.8206</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>0.459</v>
+        <v>0.5562</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>SCR-17</t>
-        </is>
+          <t>SCR-06</t>
+        </is>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -554,48 +562,51 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8943</v>
+        <v>0.6462</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0398</v>
+        <v>0.0188</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8595</v>
+        <v>0.6149</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0261</v>
+        <v>0.1502</v>
       </c>
       <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="J3" t="n">
         <v>22</v>
       </c>
-      <c r="H3" t="n">
-        <v>0.2907</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.0112</v>
-      </c>
-      <c r="J3" t="n">
-        <v>8</v>
-      </c>
       <c r="K3" t="n">
-        <v>0.2907</v>
+        <v>0.4864</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N3" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>LSC-56</t>
-        </is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -603,48 +614,51 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8996</v>
+        <v>0.6189</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0387</v>
+        <v>0.0188</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8714</v>
+        <v>0.6331</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0269</v>
+        <v>0.1479</v>
       </c>
       <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4623</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="J4" t="n">
         <v>23</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.4037</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
-      </c>
       <c r="K4" t="n">
-        <v>0.4037</v>
+        <v>0.4623</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="N4" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>SCR-01</t>
-        </is>
+          <t>DR-03</t>
+        </is>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -652,48 +666,51 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.6616</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0431</v>
+        <v>0.0198</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8573</v>
+        <v>0.5709</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0271</v>
+        <v>0.1045</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4749</v>
+        <v>0.008</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0169</v>
+        <v>0.008</v>
       </c>
       <c r="J5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L5" t="n">
         <v>8</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.4749</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
       <c r="M5" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N5" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>SCR-14</t>
-        </is>
+          <t>LSC-43</t>
+        </is>
+      </c>
+      <c r="P5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -701,48 +718,51 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8939</v>
+        <v>0.6248</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0341</v>
+        <v>0.1258</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6107</v>
+        <v>0.7859</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0072</v>
+        <v>0.1404</v>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9584</v>
+        <v>0.9589</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8253</v>
+        <v>0.8227</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6107</v>
+        <v>0.6248</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="N6" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>LSC-55</t>
-        </is>
+          <t>SCR-20</t>
+        </is>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -750,48 +770,51 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8955</v>
+        <v>0.7044</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0349</v>
+        <v>0.0135</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.6208</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007</v>
+        <v>0.1508</v>
       </c>
       <c r="G7" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9596</v>
+        <v>0.5566</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8259</v>
+        <v>0.0033</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.5566</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>DR-03</t>
-        </is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -799,48 +822,51 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8621</v>
+        <v>0.7899</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0357</v>
+        <v>0.0086</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5586</v>
+        <v>0.7147</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0081</v>
+        <v>0.0452</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9558</v>
+        <v>0.5566</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8276</v>
+        <v>0.0033</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5586</v>
+        <v>0.5566</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N8" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>SCR-20</t>
-        </is>
+          <t>DR-143</t>
+        </is>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -848,48 +874,51 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7973</v>
+        <v>0.6545</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0358</v>
+        <v>0.0338</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6643</v>
+        <v>0.9233</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0086</v>
+        <v>0.0106</v>
       </c>
       <c r="G9" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9631</v>
+        <v>0.9615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8205</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6643</v>
+        <v>0.6545</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="N9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>DR-145</t>
-        </is>
+          <t>LSC-15</t>
+        </is>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -897,48 +926,51 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7587</v>
+        <v>0.5676</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0142</v>
+        <v>0.0485</v>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7981</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0137</v>
+        <v>0.0934</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9623</v>
+        <v>0.8063</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8255</v>
+        <v>0.2037</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7587</v>
+        <v>0.5676</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>LSC-15</t>
-        </is>
+          <t>DR-125</t>
+        </is>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -946,48 +978,51 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.6057</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0112</v>
+        <v>0.0463</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9083</v>
+        <v>0.8186</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0108</v>
+        <v>0.0925</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>0.947</v>
+        <v>0.828</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4562</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.6057</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>DR-125</t>
-        </is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="P11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -995,48 +1030,51 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.754</v>
+        <v>0.6341</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0133</v>
+        <v>0.047</v>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9083</v>
+        <v>0.8259</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0108</v>
+        <v>0.0945</v>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9478</v>
+        <v>0.8413</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4549</v>
+        <v>0.1984</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.754</v>
+        <v>0.6341</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>SCR-09</t>
-        </is>
+          <t>LSC-37</t>
+        </is>
+      </c>
+      <c r="P12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1044,48 +1082,51 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7214</v>
+        <v>0.058</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0114</v>
+        <v>0.058</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8918</v>
+        <v>0.038</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0105</v>
+        <v>0.038</v>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9468</v>
+        <v>0.6566</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4544</v>
+        <v>0.0341</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7214</v>
+        <v>0.038</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N13" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>LSC-37</t>
-        </is>
+          <t>SCR-02</t>
+        </is>
+      </c>
+      <c r="P13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1093,48 +1134,51 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8545</v>
+        <v>0.4638</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0119</v>
+        <v>0.0313</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>0.977</v>
+        <v>0.6736</v>
       </c>
       <c r="F14" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0606</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8927</v>
+        <v>0.857</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2301</v>
+        <v>0.1984</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8545</v>
+        <v>0.4638</v>
       </c>
       <c r="L14" t="n">
         <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="N14" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>SCR-02</t>
-        </is>
+          <t>LSC-07</t>
+        </is>
+      </c>
+      <c r="P14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1142,48 +1186,51 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7078</v>
+        <v>0.5243</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1478</v>
+        <v>0.0403</v>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.6493</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1793</v>
+        <v>0.0451</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9161</v>
+        <v>0.751</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0708</v>
+        <v>0.1509</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7078</v>
+        <v>0.5243</v>
       </c>
       <c r="L15" t="n">
         <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="N15" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>DR-141</t>
         </is>
+      </c>
+      <c r="P15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1191,48 +1238,51 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.6503</v>
+        <v>0.5222</v>
       </c>
       <c r="C16" t="n">
-        <v>0.149</v>
+        <v>0.0391</v>
       </c>
       <c r="D16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9001</v>
+        <v>0.6119</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1801</v>
+        <v>0.0455</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8988</v>
+        <v>0.747</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0708</v>
+        <v>0.1508</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6503</v>
+        <v>0.5222</v>
       </c>
       <c r="L16" t="n">
         <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="N16" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>DR-157</t>
         </is>
+      </c>
+      <c r="P16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1240,48 +1290,51 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.6385</v>
+        <v>0.6869</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1027</v>
+        <v>0.0054</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9268</v>
+        <v>0.8215</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1378</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9195</v>
+        <v>0.9241</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0848</v>
+        <v>0.0588</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6385</v>
+        <v>0.6869</v>
       </c>
       <c r="L17" t="n">
         <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N17" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>LSC-47</t>
         </is>
+      </c>
+      <c r="P17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1289,48 +1342,51 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.6439</v>
+        <v>0.5441</v>
       </c>
       <c r="C18" t="n">
-        <v>0.101</v>
+        <v>0.0045</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9182</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1324</v>
+        <v>0.0644</v>
       </c>
       <c r="G18" t="n">
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9241</v>
+        <v>0.8935</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0852</v>
+        <v>0.0604</v>
       </c>
       <c r="J18" t="n">
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6439</v>
+        <v>0.5441</v>
       </c>
       <c r="L18" t="n">
         <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="N18" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>LSC-30</t>
         </is>
+      </c>
+      <c r="P18" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1338,48 +1394,51 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6549</v>
+        <v>0.5073</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0999</v>
+        <v>0.0044</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9247</v>
+        <v>0.785</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1336</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9185</v>
+        <v>0.8918</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0854</v>
+        <v>0.062</v>
       </c>
       <c r="J19" t="n">
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6549</v>
+        <v>0.5073</v>
       </c>
       <c r="L19" t="n">
         <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="N19" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>DR-156</t>
         </is>
+      </c>
+      <c r="P19" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1387,48 +1446,51 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.6601</v>
+        <v>0.7867</v>
       </c>
       <c r="C20" t="n">
-        <v>0.098</v>
+        <v>0.0094</v>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9284</v>
+        <v>0.7841</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1293</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8994</v>
+        <v>0.8829</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="J20" t="n">
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6601</v>
+        <v>0.7841</v>
       </c>
       <c r="L20" t="n">
         <v>5</v>
       </c>
       <c r="M20" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N20" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>LSC-32</t>
         </is>
+      </c>
+      <c r="P20" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1436,48 +1498,51 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.5481</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1064</v>
+        <v>0.0086</v>
       </c>
       <c r="D21" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8697</v>
+        <v>0.7975</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1244</v>
+        <v>0.064</v>
       </c>
       <c r="G21" t="n">
         <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9087</v>
+        <v>0.9029</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09</v>
+        <v>0.0606</v>
       </c>
       <c r="J21" t="n">
         <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5481</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="L21" t="n">
         <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N21" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>LSC-48</t>
         </is>
+      </c>
+      <c r="P21" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1485,48 +1550,51 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.5739</v>
+        <v>0.4923</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1167</v>
+        <v>0.0074</v>
       </c>
       <c r="D22" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8714</v>
+        <v>0.7991</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1259</v>
+        <v>0.0649</v>
       </c>
       <c r="G22" t="n">
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9197</v>
+        <v>0.8986</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0892</v>
+        <v>0.0588</v>
       </c>
       <c r="J22" t="n">
         <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5739</v>
+        <v>0.4923</v>
       </c>
       <c r="L22" t="n">
         <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N22" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>LSC-31</t>
         </is>
+      </c>
+      <c r="P22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1534,48 +1602,51 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.5658</v>
+        <v>0.4756</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1125</v>
+        <v>0.0035</v>
       </c>
       <c r="D23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8764</v>
+        <v>0.8409</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1268</v>
+        <v>0.0124</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9424</v>
+        <v>0.9373</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0835</v>
+        <v>0.1009</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5658</v>
+        <v>0.4756</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M23" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N23" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>DR-25</t>
         </is>
+      </c>
+      <c r="P23" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1583,48 +1654,51 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.5682</v>
+        <v>0.4104</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1128</v>
+        <v>0.0034</v>
       </c>
       <c r="D24" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8788</v>
+        <v>0.9494</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1249</v>
+        <v>0.0105</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9467</v>
+        <v>0.9398</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0824</v>
+        <v>0.0998</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5682</v>
+        <v>0.4104</v>
       </c>
       <c r="L24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M24" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="N24" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>LSC-28</t>
         </is>
+      </c>
+      <c r="P24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1632,48 +1706,51 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.5834</v>
+        <v>0.4894</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1158</v>
+        <v>0.0043</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8772</v>
+        <v>0.9227</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1227</v>
+        <v>0.0108</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9397</v>
+        <v>0.9295</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0982</v>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5834</v>
+        <v>0.4894</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M25" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="N25" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>DR-110</t>
         </is>
+      </c>
+      <c r="P25" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1681,48 +1758,51 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.6137</v>
+        <v>0.636</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1233</v>
+        <v>0.0061</v>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9063</v>
+        <v>0.8359</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1273</v>
+        <v>0.0124</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9348</v>
+        <v>0.953</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0873</v>
+        <v>0.1055</v>
       </c>
       <c r="J26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6137</v>
+        <v>0.636</v>
       </c>
       <c r="L26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M26" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="N26" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>LSC-46</t>
         </is>
+      </c>
+      <c r="P26" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1730,48 +1810,51 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.6362</v>
+        <v>0.662</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1216</v>
+        <v>0.0068</v>
       </c>
       <c r="D27" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9071</v>
+        <v>0.8408</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1273</v>
+        <v>0.013</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9281</v>
+        <v>0.9517</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0868</v>
+        <v>0.1008</v>
       </c>
       <c r="J27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.6362</v>
+        <v>0.662</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N27" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>LSC-35</t>
         </is>
+      </c>
+      <c r="P27" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1779,48 +1862,51 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7016</v>
+        <v>0.6412</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1228</v>
+        <v>0.0055</v>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9097</v>
+        <v>0.86</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1281</v>
+        <v>0.0131</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9392</v>
+        <v>0.9584</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0861</v>
+        <v>0.1</v>
       </c>
       <c r="J28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7016</v>
+        <v>0.6412</v>
       </c>
       <c r="L28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="N28" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>LSC-29</t>
         </is>
+      </c>
+      <c r="P28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1828,48 +1914,51 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.7618</v>
+        <v>0.4573</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1304</v>
+        <v>0.0035</v>
       </c>
       <c r="D29" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9143</v>
+        <v>0.9016</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1327</v>
+        <v>0.0136</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9031</v>
+        <v>0.947</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0905</v>
+        <v>0.0581</v>
       </c>
       <c r="J29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7618</v>
+        <v>0.4573</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="N29" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>SCR-12</t>
         </is>
+      </c>
+      <c r="P29" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1877,48 +1966,51 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.7692</v>
+        <v>0.038</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0201</v>
+        <v>0.038</v>
       </c>
       <c r="D30" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9213</v>
+        <v>0.9107</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1351</v>
+        <v>0.0135</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8657</v>
+        <v>0.841</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0354</v>
+        <v>0.0117</v>
       </c>
       <c r="J30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7692</v>
+        <v>0.038</v>
       </c>
       <c r="L30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M30" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N30" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>DR-71</t>
         </is>
+      </c>
+      <c r="P30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1926,48 +2018,51 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.8106</v>
+        <v>0.5457</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0191</v>
+        <v>0.0042</v>
       </c>
       <c r="D31" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9127</v>
+        <v>0.9383</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1382</v>
+        <v>0.0136</v>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8884</v>
+        <v>0.9643</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0318</v>
+        <v>0.067</v>
       </c>
       <c r="J31" t="n">
         <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8106</v>
+        <v>0.5457</v>
       </c>
       <c r="L31" t="n">
         <v>7</v>
       </c>
       <c r="M31" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="N31" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>DR-123</t>
         </is>
+      </c>
+      <c r="P31" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1975,293 +2070,51 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.6827</v>
+        <v>0.4519</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0176</v>
+        <v>0.0035</v>
       </c>
       <c r="D32" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9064</v>
+        <v>0.9272</v>
       </c>
       <c r="F32" t="n">
-        <v>0.137</v>
+        <v>0.0101</v>
       </c>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8552</v>
+        <v>0.9683</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0309</v>
+        <v>0.0677</v>
       </c>
       <c r="J32" t="n">
         <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6827</v>
+        <v>0.4519</v>
       </c>
       <c r="L32" t="n">
         <v>7</v>
       </c>
       <c r="M32" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N32" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>DR-140</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0.5024</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.0164</v>
-      </c>
-      <c r="D33" t="n">
-        <v>48</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.9675</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.0483</v>
-      </c>
-      <c r="G33" t="n">
-        <v>10</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.6824</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0171</v>
-      </c>
-      <c r="J33" t="n">
-        <v>8</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.5024</v>
-      </c>
-      <c r="L33" t="n">
-        <v>8</v>
-      </c>
-      <c r="M33" t="n">
-        <v>66</v>
-      </c>
-      <c r="N33" t="n">
-        <v>66</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>LSC-44</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0.6002</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.0164</v>
-      </c>
-      <c r="D34" t="n">
-        <v>15</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.7983</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.0069</v>
-      </c>
-      <c r="G34" t="n">
-        <v>48</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.8064</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.3925</v>
-      </c>
-      <c r="J34" t="n">
-        <v>4</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.6002</v>
-      </c>
-      <c r="L34" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="n">
-        <v>67</v>
-      </c>
-      <c r="N34" t="n">
-        <v>67</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>DR-130</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0.8911</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="D35" t="n">
-        <v>51</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.7156</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="G35" t="n">
-        <v>6</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.7879</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.0646</v>
-      </c>
-      <c r="J35" t="n">
-        <v>11</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.7156</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6</v>
-      </c>
-      <c r="M35" t="n">
-        <v>68</v>
-      </c>
-      <c r="N35" t="n">
-        <v>68</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>DR-129</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0.8819</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D36" t="n">
-        <v>52</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.7171999999999999</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.0192</v>
-      </c>
-      <c r="G36" t="n">
-        <v>6</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.7663</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.0643</v>
-      </c>
-      <c r="J36" t="n">
-        <v>11</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.7171999999999999</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6</v>
-      </c>
-      <c r="M36" t="n">
-        <v>69</v>
-      </c>
-      <c r="N36" t="n">
-        <v>69</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>LSC-51</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="n">
-        <v>0.8699</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.0397</v>
-      </c>
-      <c r="D37" t="n">
-        <v>53</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.0183</v>
-      </c>
-      <c r="G37" t="n">
-        <v>6</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.7717000000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.0621</v>
-      </c>
-      <c r="J37" t="n">
-        <v>11</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="L37" t="n">
-        <v>6</v>
-      </c>
-      <c r="M37" t="n">
-        <v>70</v>
-      </c>
-      <c r="N37" t="n">
-        <v>70</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>LSC-01</t>
-        </is>
+      <c r="P32" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
